--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:39</t>
+    <t xml:space="preserve">2026-09-10 00:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:48</t>
+    <t xml:space="preserve">2026-09-18 10:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
@@ -180,18 +180,18 @@
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
+    <t xml:space="preserve">Estación Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Providencia</t>
   </si>
   <si>
     <t xml:space="preserve">Vitacura</t>
   </si>
   <si>
-    <t xml:space="preserve">Estación Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:57</t>
+    <t xml:space="preserve">2026-09-23 14:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1447,9 +1447,11 @@
         <v>54</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>13123</v>
-      </c>
-      <c r="D50" s="2"/>
+        <v>13106</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
@@ -1460,9 +1462,11 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>13132</v>
-      </c>
-      <c r="D51" s="2"/>
+        <v>13114</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
@@ -1473,9 +1477,11 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13106</v>
-      </c>
-      <c r="D52" s="2"/>
+        <v>13123</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
@@ -1486,9 +1492,11 @@
         <v>57</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>13114</v>
-      </c>
-      <c r="D53" s="2"/>
+        <v>13132</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:17</t>
+    <t xml:space="preserve">2026-10-02 15:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:36</t>
+    <t xml:space="preserve">2026-10-05 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
